--- a/public/example/business_area_template.xlsx
+++ b/public/example/business_area_template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\html-tool\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78A3E04-626A-4002-AA6D-F25FA360925D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73858087-3FE4-498A-A5A0-BA22F3A020A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9270" yWindow="3480" windowWidth="18855" windowHeight="15345" xr2:uid="{261C27C1-C7AF-5A4F-A7E5-AF5696E507EF}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{261C27C1-C7AF-5A4F-A7E5-AF5696E507EF}"/>
   </bookViews>
   <sheets>
-    <sheet name="global_en" sheetId="1" r:id="rId1"/>
+    <sheet name="global" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/public/example/business_area_template.xlsx
+++ b/public/example/business_area_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\html-tool\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73858087-3FE4-498A-A5A0-BA22F3A020A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8262CF8-55B9-4014-8287-E0E2C0B4407C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{261C27C1-C7AF-5A4F-A7E5-AF5696E507EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{261C27C1-C7AF-5A4F-A7E5-AF5696E507EF}"/>
   </bookViews>
   <sheets>
     <sheet name="global" sheetId="1" r:id="rId1"/>
@@ -249,9 +249,6 @@
     <t>Automotive Display</t>
   </si>
   <si>
-    <t>Safety &amp; Comport</t>
-  </si>
-  <si>
     <t>Transformative &amp; Dynamic</t>
   </si>
   <si>
@@ -386,6 +383,10 @@
   </si>
   <si>
     <t>Built to Think. Designed to Move.</t>
+  </si>
+  <si>
+    <t>Safety &amp; Comfort</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1101,16 +1102,16 @@
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>96</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1131,7 +1132,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="B4" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>5</v>
@@ -1174,16 +1175,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="F6" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="G6" s="18" t="s">
         <v>101</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="78.75">
@@ -1196,10 +1197,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>83</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>58</v>
@@ -1227,7 +1228,7 @@
     <row r="9" spans="1:8">
       <c r="A9" s="2"/>
       <c r="B9" s="25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>10</v>
@@ -1242,7 +1243,7 @@
         <v>52</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -1253,16 +1254,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="F10" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="G10" s="18" t="s">
         <v>105</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>106</v>
       </c>
       <c r="H10" s="9"/>
     </row>
@@ -1276,7 +1277,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>56</v>
@@ -1376,7 +1377,7 @@
     <row r="17" spans="1:7">
       <c r="A17" s="2"/>
       <c r="B17" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>10</v>
@@ -1401,16 +1402,16 @@
         <v>6</v>
       </c>
       <c r="D18" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="F18" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="G18" s="18" t="s">
         <v>109</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="45">
@@ -1420,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E19" s="20" t="s">
         <v>54</v>
@@ -1442,13 +1443,13 @@
         <v>16</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1459,13 +1460,13 @@
         <v>18</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>34</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1476,7 +1477,7 @@
         <v>19</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>35</v>
@@ -1505,7 +1506,7 @@
     <row r="24" spans="1:7">
       <c r="A24" s="2"/>
       <c r="B24" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>10</v>
@@ -1520,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1533,13 +1534,13 @@
         <v>25</v>
       </c>
       <c r="E25" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="20" t="s">
         <v>111</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="112.15" customHeight="1">
@@ -1552,7 +1553,7 @@
         <v>66</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>0</v>
@@ -1614,7 +1615,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="B30" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>10</v>
@@ -1641,13 +1642,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="18" t="s">
         <v>113</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="97.9" customHeight="1">
@@ -1659,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>0</v>
@@ -1704,7 +1705,7 @@
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>10</v>
@@ -1713,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>0</v>
@@ -1729,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>0</v>
@@ -1761,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>0</v>
@@ -1775,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>0</v>
@@ -1789,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>0</v>
@@ -1803,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>0</v>
@@ -1817,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>0</v>

--- a/public/example/business_area_template.xlsx
+++ b/public/example/business_area_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\html-tool\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8262CF8-55B9-4014-8287-E0E2C0B4407C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC54A2E-21C9-4A6C-B094-ACAEFF94E104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{261C27C1-C7AF-5A4F-A7E5-AF5696E507EF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="139">
   <si>
     <t>N/A</t>
   </si>
@@ -386,6 +386,98 @@
   </si>
   <si>
     <t>Safety &amp; Comfort</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>play video</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>pause video</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>previous slide</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>next slide</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tab label</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>More button</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Video label</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Video alt</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eco Solution video</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eco Solution video thumbnail</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vehicle Solution video</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vehicle Solution video thumbnail</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>media entertainment solution video</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>media entertainment solution video thumbnail</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>home appliance solution video</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>home appliance solution video thumbnail</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>If you select menu, the focus move to area providing the selected information in this web page.</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Learn more</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Play video</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pause video</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Previous Slide</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Next Slide</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -532,7 +624,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -649,12 +741,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -716,9 +845,21 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -729,6 +870,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1080,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0030AE-E3AA-A242-946D-BB5D90FAE15A}">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="17.25"/>
   <cols>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -1097,10 +1247,10 @@
       <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="14" t="s">
         <v>93</v>
       </c>
@@ -1115,8 +1265,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="14" t="s">
         <v>24</v>
       </c>
@@ -1131,7 +1281,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="35" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="8" t="s">
@@ -1151,7 +1301,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="B5" s="29"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="8" t="s">
         <v>4</v>
       </c>
@@ -1170,7 +1320,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1"/>
-      <c r="B6" s="29"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="8" t="s">
         <v>3</v>
       </c>
@@ -1189,7 +1339,7 @@
     </row>
     <row r="7" spans="1:8" ht="78.75">
       <c r="A7" s="2"/>
-      <c r="B7" s="29"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="15" t="s">
         <v>2</v>
       </c>
@@ -1206,135 +1356,139 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="19.5">
+    <row r="8" spans="1:8">
       <c r="A8" s="2"/>
-      <c r="B8" s="30"/>
+      <c r="B8" s="36"/>
       <c r="C8" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2"/>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="36"/>
+      <c r="C9" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="19.5">
+      <c r="A10" s="2"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2"/>
+      <c r="B11" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F11" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G11" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="H9" s="11"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="3"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="8" t="s">
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="3"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D12" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E12" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F12" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G12" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:8" ht="56.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="8" t="s">
+      <c r="H12" s="9"/>
+    </row>
+    <row r="13" spans="1:8" ht="56.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E13" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F13" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G13" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>0</v>
-      </c>
+      <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="30" t="s">
+        <v>7</v>
+      </c>
       <c r="D14" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>39</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>0</v>
@@ -1342,16 +1496,16 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>0</v>
@@ -1359,16 +1513,16 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="26"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="F16" s="12" t="s">
-        <v>0</v>
+      <c r="F16" s="18" t="s">
+        <v>31</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>0</v>
@@ -1376,469 +1530,584 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2"/>
-      <c r="B17" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>10</v>
-      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="30"/>
       <c r="D17" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>69</v>
+        <v>15</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>0</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>45</v>
+        <v>32</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="8" t="s">
-        <v>6</v>
-      </c>
+      <c r="B18" s="34"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="45">
+        <v>16</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="2"/>
-      <c r="B19" s="25"/>
+      <c r="B19" s="29" t="s">
+        <v>89</v>
+      </c>
       <c r="C19" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>61</v>
+        <v>10</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="26" t="s">
-        <v>7</v>
+      <c r="B20" s="29"/>
+      <c r="C20" s="8" t="s">
+        <v>6</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="45">
       <c r="A21" s="2"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>85</v>
+      <c r="B21" s="29"/>
+      <c r="C21" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="26"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="30" t="s">
+        <v>7</v>
+      </c>
       <c r="D22" s="17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="26"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="30"/>
       <c r="D23" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>70</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2"/>
-      <c r="B24" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>10</v>
-      </c>
+      <c r="B24" s="29"/>
+      <c r="C24" s="30"/>
       <c r="D24" s="17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>35</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="8" t="s">
+      <c r="B25" s="29"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2"/>
+      <c r="B26" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D27" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E27" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" s="20" t="s">
+      <c r="F27" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27" s="20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="112.15" customHeight="1">
-      <c r="A26" s="2"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="8" t="s">
+    <row r="28" spans="1:7" ht="112.15" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D28" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E28" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" s="20" t="s">
+      <c r="F28" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="4"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="26" t="s">
+    <row r="29" spans="1:7">
+      <c r="A29" s="4"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D29" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E29" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" s="18" t="s">
+      <c r="F29" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29" s="18" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="B28" s="25"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="17" t="s">
+    <row r="30" spans="1:7">
+      <c r="B30" s="29"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E30" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="18" t="s">
+      <c r="F30" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" s="18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="B29" s="25"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G29" s="18" t="s">
+    <row r="31" spans="1:7">
+      <c r="B31" s="29"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="25" t="s">
+    <row r="32" spans="1:7">
+      <c r="B32" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C32" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E30" s="18" t="s">
+      <c r="D32" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" s="18" t="s">
+      <c r="F32" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" s="18" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="B31" s="25"/>
-      <c r="C31" s="8" t="s">
+    <row r="33" spans="2:7">
+      <c r="B33" s="29"/>
+      <c r="C33" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E31" s="18" t="s">
+      <c r="D33" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E33" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" s="18" t="s">
+      <c r="F33" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" s="18" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="97.9" customHeight="1">
-      <c r="B32" s="25"/>
-      <c r="C32" s="8" t="s">
+    <row r="34" spans="2:7" ht="97.9" customHeight="1">
+      <c r="B34" s="29"/>
+      <c r="C34" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E32" s="20" t="s">
+      <c r="D34" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F32" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G32" s="20" t="s">
+      <c r="F34" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G34" s="20" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="25"/>
-      <c r="C33" s="26" t="s">
+    <row r="35" spans="2:7">
+      <c r="B35" s="29"/>
+      <c r="C35" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E33" s="18" t="s">
+      <c r="D35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G33" s="18" t="s">
+      <c r="F35" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G35" s="18" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="25"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E34" s="18" t="s">
+    <row r="36" spans="2:7">
+      <c r="B36" s="29"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E36" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="F34" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G34" s="18" t="s">
+      <c r="F36" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" s="18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="23" t="s">
+    <row r="37" spans="2:7">
+      <c r="B37" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C37" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E35" s="18" t="s">
+      <c r="D37" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G35" s="12"/>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="23"/>
-      <c r="C36" s="13" t="s">
+      <c r="F37" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="24"/>
+      <c r="C38" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D36" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E36" s="20" t="s">
+      <c r="D38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="37" spans="2:7" ht="45">
-      <c r="B37" s="23"/>
-      <c r="C37" s="13" t="s">
+      <c r="F38" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" spans="2:7" ht="45">
+      <c r="B39" s="24"/>
+      <c r="C39" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E37" s="20" t="s">
+      <c r="D39" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E39" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G37" s="12"/>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="23"/>
-      <c r="C38" s="24" t="s">
+      <c r="F39" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="24"/>
+      <c r="C40" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E38" s="18" t="s">
+      <c r="D40" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G38" s="12"/>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="23"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E39" s="18" t="s">
+      <c r="F40" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12"/>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="24"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E41" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G39" s="12"/>
-    </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="23"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E40" s="18" t="s">
+      <c r="F41" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12"/>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="24"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E42" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="F40" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G40" s="12"/>
-    </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="23"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E41" s="18" t="s">
+      <c r="F42" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12"/>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="24"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E43" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F41" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G41" s="16"/>
-    </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="23"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E42" s="18" t="s">
+      <c r="F43" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G43" s="16"/>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="24"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E44" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F42" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G42" s="12"/>
+      <c r="F44" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G44" s="12"/>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="27"/>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="24"/>
+      <c r="C46" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="27"/>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="24"/>
+      <c r="C47" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="27"/>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="24"/>
+      <c r="C48" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="27"/>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="24"/>
+      <c r="C49" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="27"/>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="24"/>
+      <c r="C50" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B35:B42"/>
-    <mergeCell ref="C38:C42"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="C33:C34"/>
+  <mergeCells count="19">
+    <mergeCell ref="B37:B44"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="C35:C36"/>
     <mergeCell ref="B2:C3"/>
-    <mergeCell ref="B9:B16"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="B24:B29"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B11:B18"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="B45:B50"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="D49:G49"/>
+    <mergeCell ref="D50:G50"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
